--- a/excel/Vacation_S1.xlsx
+++ b/excel/Vacation_S1.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="52">
   <si>
     <t>Acteur Dépense</t>
   </si>
@@ -141,6 +141,33 @@
   </si>
   <si>
     <t/>
+  </si>
+  <si>
+    <t>12/08/2026</t>
+  </si>
+  <si>
+    <t>0987</t>
+  </si>
+  <si>
+    <t>TEST 1</t>
+  </si>
+  <si>
+    <t>TO</t>
+  </si>
+  <si>
+    <t>15/08/2026</t>
+  </si>
+  <si>
+    <t>002</t>
+  </si>
+  <si>
+    <t>111</t>
+  </si>
+  <si>
+    <t>1110000000000000</t>
+  </si>
+  <si>
+    <t>00</t>
   </si>
 </sst>
 </file>
@@ -213,9 +240,21 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="true" applyAlignment="true" applyFill="true" applyBorder="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyAlignment="true" applyFill="true" applyBorder="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="4" borderId="4" xfId="0" applyAlignment="true" applyFill="true" applyBorder="true" applyNumberFormat="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyAlignment="true" applyFill="true" applyBorder="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="4" borderId="4" xfId="0" applyAlignment="true" applyFill="true" applyBorder="true" applyNumberFormat="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyAlignment="true" applyFill="true" applyBorder="true">
@@ -242,7 +281,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:T7"/>
+  <dimension ref="A1:T9"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" bestFit="true" customWidth="true" width="13.98046875"/>
@@ -550,6 +589,130 @@
         <v>42</v>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" t="s" s="8">
+        <v>31</v>
+      </c>
+      <c r="B8" t="s" s="8">
+        <v>43</v>
+      </c>
+      <c r="C8" t="s" s="8">
+        <v>33</v>
+      </c>
+      <c r="D8" t="n" s="8">
+        <v>50.0</v>
+      </c>
+      <c r="E8" t="n" s="8">
+        <v>156.0</v>
+      </c>
+      <c r="F8" t="n" s="8">
+        <v>7800.0</v>
+      </c>
+      <c r="G8" t="n" s="8">
+        <v>2886.0</v>
+      </c>
+      <c r="H8" t="n" s="8">
+        <v>4914.0</v>
+      </c>
+      <c r="I8" t="s" s="9">
+        <v>44</v>
+      </c>
+      <c r="J8" t="s" s="8">
+        <v>45</v>
+      </c>
+      <c r="K8" t="s" s="8">
+        <v>46</v>
+      </c>
+      <c r="L8" t="s" s="8">
+        <v>47</v>
+      </c>
+      <c r="M8" t="s" s="8">
+        <v>35</v>
+      </c>
+      <c r="N8" t="s" s="8">
+        <v>36</v>
+      </c>
+      <c r="O8" t="s" s="9">
+        <v>48</v>
+      </c>
+      <c r="P8" t="s" s="9">
+        <v>49</v>
+      </c>
+      <c r="Q8" t="s" s="9">
+        <v>50</v>
+      </c>
+      <c r="R8" t="s" s="9">
+        <v>51</v>
+      </c>
+      <c r="S8" t="s" s="8">
+        <v>41</v>
+      </c>
+      <c r="T8" t="s" s="8">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s" s="10">
+        <v>31</v>
+      </c>
+      <c r="B9" t="s" s="10">
+        <v>43</v>
+      </c>
+      <c r="C9" t="s" s="10">
+        <v>33</v>
+      </c>
+      <c r="D9" t="n" s="10">
+        <v>50.0</v>
+      </c>
+      <c r="E9" t="n" s="10">
+        <v>156.0</v>
+      </c>
+      <c r="F9" t="n" s="10">
+        <v>7800.0</v>
+      </c>
+      <c r="G9" t="n" s="10">
+        <v>2886.0</v>
+      </c>
+      <c r="H9" t="n" s="10">
+        <v>4914.0</v>
+      </c>
+      <c r="I9" t="s" s="11">
+        <v>44</v>
+      </c>
+      <c r="J9" t="s" s="10">
+        <v>45</v>
+      </c>
+      <c r="K9" t="s" s="10">
+        <v>46</v>
+      </c>
+      <c r="L9" t="s" s="10">
+        <v>47</v>
+      </c>
+      <c r="M9" t="s" s="10">
+        <v>35</v>
+      </c>
+      <c r="N9" t="s" s="10">
+        <v>36</v>
+      </c>
+      <c r="O9" t="s" s="11">
+        <v>48</v>
+      </c>
+      <c r="P9" t="s" s="11">
+        <v>49</v>
+      </c>
+      <c r="Q9" t="s" s="11">
+        <v>50</v>
+      </c>
+      <c r="R9" t="s" s="11">
+        <v>51</v>
+      </c>
+      <c r="S9" t="s" s="10">
+        <v>42</v>
+      </c>
+      <c r="T9" t="s" s="10">
+        <v>42</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>

--- a/excel/Vacation_S1.xlsx
+++ b/excel/Vacation_S1.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="256" uniqueCount="52">
   <si>
     <t>Acteur Dépense</t>
   </si>
@@ -240,9 +240,69 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="true" applyAlignment="true" applyFill="true" applyBorder="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyAlignment="true" applyFill="true" applyBorder="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="4" borderId="4" xfId="0" applyAlignment="true" applyFill="true" applyBorder="true" applyNumberFormat="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyAlignment="true" applyFill="true" applyBorder="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="4" borderId="4" xfId="0" applyAlignment="true" applyFill="true" applyBorder="true" applyNumberFormat="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyAlignment="true" applyFill="true" applyBorder="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="4" borderId="4" xfId="0" applyAlignment="true" applyFill="true" applyBorder="true" applyNumberFormat="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyAlignment="true" applyFill="true" applyBorder="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="4" borderId="4" xfId="0" applyAlignment="true" applyFill="true" applyBorder="true" applyNumberFormat="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyAlignment="true" applyFill="true" applyBorder="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="4" borderId="4" xfId="0" applyAlignment="true" applyFill="true" applyBorder="true" applyNumberFormat="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyAlignment="true" applyFill="true" applyBorder="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="4" borderId="4" xfId="0" applyAlignment="true" applyFill="true" applyBorder="true" applyNumberFormat="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyAlignment="true" applyFill="true" applyBorder="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="4" borderId="4" xfId="0" applyAlignment="true" applyFill="true" applyBorder="true" applyNumberFormat="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyAlignment="true" applyFill="true" applyBorder="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="4" borderId="4" xfId="0" applyAlignment="true" applyFill="true" applyBorder="true" applyNumberFormat="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyAlignment="true" applyFill="true" applyBorder="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="4" borderId="4" xfId="0" applyAlignment="true" applyFill="true" applyBorder="true" applyNumberFormat="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyAlignment="true" applyFill="true" applyBorder="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="4" borderId="4" xfId="0" applyAlignment="true" applyFill="true" applyBorder="true" applyNumberFormat="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyAlignment="true" applyFill="true" applyBorder="true">
@@ -281,7 +341,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:T9"/>
+  <dimension ref="A1:T19"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" bestFit="true" customWidth="true" width="13.98046875"/>
@@ -713,6 +773,626 @@
         <v>42</v>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" t="s" s="12">
+        <v>31</v>
+      </c>
+      <c r="B10" t="s" s="12">
+        <v>43</v>
+      </c>
+      <c r="C10" t="s" s="12">
+        <v>33</v>
+      </c>
+      <c r="D10" t="n" s="12">
+        <v>50.0</v>
+      </c>
+      <c r="E10" t="n" s="12">
+        <v>156.0</v>
+      </c>
+      <c r="F10" t="n" s="12">
+        <v>7800.0</v>
+      </c>
+      <c r="G10" t="n" s="12">
+        <v>2886.0</v>
+      </c>
+      <c r="H10" t="n" s="12">
+        <v>4914.0</v>
+      </c>
+      <c r="I10" t="s" s="13">
+        <v>44</v>
+      </c>
+      <c r="J10" t="s" s="12">
+        <v>45</v>
+      </c>
+      <c r="K10" t="s" s="12">
+        <v>46</v>
+      </c>
+      <c r="L10" t="s" s="12">
+        <v>47</v>
+      </c>
+      <c r="M10" t="s" s="12">
+        <v>35</v>
+      </c>
+      <c r="N10" t="s" s="12">
+        <v>36</v>
+      </c>
+      <c r="O10" t="s" s="13">
+        <v>48</v>
+      </c>
+      <c r="P10" t="s" s="13">
+        <v>49</v>
+      </c>
+      <c r="Q10" t="s" s="13">
+        <v>50</v>
+      </c>
+      <c r="R10" t="s" s="13">
+        <v>51</v>
+      </c>
+      <c r="S10" t="s" s="12">
+        <v>41</v>
+      </c>
+      <c r="T10" t="s" s="12">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s" s="14">
+        <v>31</v>
+      </c>
+      <c r="B11" t="s" s="14">
+        <v>43</v>
+      </c>
+      <c r="C11" t="s" s="14">
+        <v>33</v>
+      </c>
+      <c r="D11" t="n" s="14">
+        <v>50.0</v>
+      </c>
+      <c r="E11" t="n" s="14">
+        <v>156.0</v>
+      </c>
+      <c r="F11" t="n" s="14">
+        <v>7800.0</v>
+      </c>
+      <c r="G11" t="n" s="14">
+        <v>2886.0</v>
+      </c>
+      <c r="H11" t="n" s="14">
+        <v>4914.0</v>
+      </c>
+      <c r="I11" t="s" s="15">
+        <v>44</v>
+      </c>
+      <c r="J11" t="s" s="14">
+        <v>45</v>
+      </c>
+      <c r="K11" t="s" s="14">
+        <v>46</v>
+      </c>
+      <c r="L11" t="s" s="14">
+        <v>47</v>
+      </c>
+      <c r="M11" t="s" s="14">
+        <v>35</v>
+      </c>
+      <c r="N11" t="s" s="14">
+        <v>36</v>
+      </c>
+      <c r="O11" t="s" s="15">
+        <v>48</v>
+      </c>
+      <c r="P11" t="s" s="15">
+        <v>49</v>
+      </c>
+      <c r="Q11" t="s" s="15">
+        <v>50</v>
+      </c>
+      <c r="R11" t="s" s="15">
+        <v>51</v>
+      </c>
+      <c r="S11" t="s" s="14">
+        <v>41</v>
+      </c>
+      <c r="T11" t="s" s="14">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s" s="16">
+        <v>31</v>
+      </c>
+      <c r="B12" t="s" s="16">
+        <v>43</v>
+      </c>
+      <c r="C12" t="s" s="16">
+        <v>33</v>
+      </c>
+      <c r="D12" t="n" s="16">
+        <v>50.0</v>
+      </c>
+      <c r="E12" t="n" s="16">
+        <v>156.0</v>
+      </c>
+      <c r="F12" t="n" s="16">
+        <v>7800.0</v>
+      </c>
+      <c r="G12" t="n" s="16">
+        <v>2886.0</v>
+      </c>
+      <c r="H12" t="n" s="16">
+        <v>4914.0</v>
+      </c>
+      <c r="I12" t="s" s="17">
+        <v>44</v>
+      </c>
+      <c r="J12" t="s" s="16">
+        <v>45</v>
+      </c>
+      <c r="K12" t="s" s="16">
+        <v>46</v>
+      </c>
+      <c r="L12" t="s" s="16">
+        <v>47</v>
+      </c>
+      <c r="M12" t="s" s="16">
+        <v>35</v>
+      </c>
+      <c r="N12" t="s" s="16">
+        <v>36</v>
+      </c>
+      <c r="O12" t="s" s="17">
+        <v>48</v>
+      </c>
+      <c r="P12" t="s" s="17">
+        <v>49</v>
+      </c>
+      <c r="Q12" t="s" s="17">
+        <v>50</v>
+      </c>
+      <c r="R12" t="s" s="17">
+        <v>51</v>
+      </c>
+      <c r="S12" t="s" s="16">
+        <v>42</v>
+      </c>
+      <c r="T12" t="s" s="16">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s" s="18">
+        <v>31</v>
+      </c>
+      <c r="B13" t="s" s="18">
+        <v>43</v>
+      </c>
+      <c r="C13" t="s" s="18">
+        <v>33</v>
+      </c>
+      <c r="D13" t="n" s="18">
+        <v>50.0</v>
+      </c>
+      <c r="E13" t="n" s="18">
+        <v>156.0</v>
+      </c>
+      <c r="F13" t="n" s="18">
+        <v>7800.0</v>
+      </c>
+      <c r="G13" t="n" s="18">
+        <v>2886.0</v>
+      </c>
+      <c r="H13" t="n" s="18">
+        <v>4914.0</v>
+      </c>
+      <c r="I13" t="s" s="19">
+        <v>44</v>
+      </c>
+      <c r="J13" t="s" s="18">
+        <v>45</v>
+      </c>
+      <c r="K13" t="s" s="18">
+        <v>46</v>
+      </c>
+      <c r="L13" t="s" s="18">
+        <v>47</v>
+      </c>
+      <c r="M13" t="s" s="18">
+        <v>35</v>
+      </c>
+      <c r="N13" t="s" s="18">
+        <v>36</v>
+      </c>
+      <c r="O13" t="s" s="19">
+        <v>48</v>
+      </c>
+      <c r="P13" t="s" s="19">
+        <v>49</v>
+      </c>
+      <c r="Q13" t="s" s="19">
+        <v>50</v>
+      </c>
+      <c r="R13" t="s" s="19">
+        <v>51</v>
+      </c>
+      <c r="S13" t="s" s="18">
+        <v>41</v>
+      </c>
+      <c r="T13" t="s" s="18">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s" s="20">
+        <v>31</v>
+      </c>
+      <c r="B14" t="s" s="20">
+        <v>43</v>
+      </c>
+      <c r="C14" t="s" s="20">
+        <v>33</v>
+      </c>
+      <c r="D14" t="n" s="20">
+        <v>50.0</v>
+      </c>
+      <c r="E14" t="n" s="20">
+        <v>156.0</v>
+      </c>
+      <c r="F14" t="n" s="20">
+        <v>7800.0</v>
+      </c>
+      <c r="G14" t="n" s="20">
+        <v>2886.0</v>
+      </c>
+      <c r="H14" t="n" s="20">
+        <v>4914.0</v>
+      </c>
+      <c r="I14" t="s" s="21">
+        <v>44</v>
+      </c>
+      <c r="J14" t="s" s="20">
+        <v>45</v>
+      </c>
+      <c r="K14" t="s" s="20">
+        <v>46</v>
+      </c>
+      <c r="L14" t="s" s="20">
+        <v>47</v>
+      </c>
+      <c r="M14" t="s" s="20">
+        <v>35</v>
+      </c>
+      <c r="N14" t="s" s="20">
+        <v>36</v>
+      </c>
+      <c r="O14" t="s" s="21">
+        <v>48</v>
+      </c>
+      <c r="P14" t="s" s="21">
+        <v>49</v>
+      </c>
+      <c r="Q14" t="s" s="21">
+        <v>50</v>
+      </c>
+      <c r="R14" t="s" s="21">
+        <v>51</v>
+      </c>
+      <c r="S14" t="s" s="20">
+        <v>41</v>
+      </c>
+      <c r="T14" t="s" s="20">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s" s="22">
+        <v>31</v>
+      </c>
+      <c r="B15" t="s" s="22">
+        <v>43</v>
+      </c>
+      <c r="C15" t="s" s="22">
+        <v>33</v>
+      </c>
+      <c r="D15" t="n" s="22">
+        <v>50.0</v>
+      </c>
+      <c r="E15" t="n" s="22">
+        <v>156.0</v>
+      </c>
+      <c r="F15" t="n" s="22">
+        <v>7800.0</v>
+      </c>
+      <c r="G15" t="n" s="22">
+        <v>2886.0</v>
+      </c>
+      <c r="H15" t="n" s="22">
+        <v>4914.0</v>
+      </c>
+      <c r="I15" t="s" s="23">
+        <v>44</v>
+      </c>
+      <c r="J15" t="s" s="22">
+        <v>45</v>
+      </c>
+      <c r="K15" t="s" s="22">
+        <v>46</v>
+      </c>
+      <c r="L15" t="s" s="22">
+        <v>47</v>
+      </c>
+      <c r="M15" t="s" s="22">
+        <v>35</v>
+      </c>
+      <c r="N15" t="s" s="22">
+        <v>36</v>
+      </c>
+      <c r="O15" t="s" s="23">
+        <v>48</v>
+      </c>
+      <c r="P15" t="s" s="23">
+        <v>49</v>
+      </c>
+      <c r="Q15" t="s" s="23">
+        <v>50</v>
+      </c>
+      <c r="R15" t="s" s="23">
+        <v>51</v>
+      </c>
+      <c r="S15" t="s" s="22">
+        <v>41</v>
+      </c>
+      <c r="T15" t="s" s="22">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s" s="24">
+        <v>31</v>
+      </c>
+      <c r="B16" t="s" s="24">
+        <v>43</v>
+      </c>
+      <c r="C16" t="s" s="24">
+        <v>33</v>
+      </c>
+      <c r="D16" t="n" s="24">
+        <v>50.0</v>
+      </c>
+      <c r="E16" t="n" s="24">
+        <v>156.0</v>
+      </c>
+      <c r="F16" t="n" s="24">
+        <v>7800.0</v>
+      </c>
+      <c r="G16" t="n" s="24">
+        <v>2886.0</v>
+      </c>
+      <c r="H16" t="n" s="24">
+        <v>4914.0</v>
+      </c>
+      <c r="I16" t="s" s="25">
+        <v>44</v>
+      </c>
+      <c r="J16" t="s" s="24">
+        <v>45</v>
+      </c>
+      <c r="K16" t="s" s="24">
+        <v>46</v>
+      </c>
+      <c r="L16" t="s" s="24">
+        <v>47</v>
+      </c>
+      <c r="M16" t="s" s="24">
+        <v>35</v>
+      </c>
+      <c r="N16" t="s" s="24">
+        <v>36</v>
+      </c>
+      <c r="O16" t="s" s="25">
+        <v>48</v>
+      </c>
+      <c r="P16" t="s" s="25">
+        <v>49</v>
+      </c>
+      <c r="Q16" t="s" s="25">
+        <v>50</v>
+      </c>
+      <c r="R16" t="s" s="25">
+        <v>51</v>
+      </c>
+      <c r="S16" t="s" s="24">
+        <v>41</v>
+      </c>
+      <c r="T16" t="s" s="24">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s" s="26">
+        <v>31</v>
+      </c>
+      <c r="B17" t="s" s="26">
+        <v>43</v>
+      </c>
+      <c r="C17" t="s" s="26">
+        <v>33</v>
+      </c>
+      <c r="D17" t="n" s="26">
+        <v>50.0</v>
+      </c>
+      <c r="E17" t="n" s="26">
+        <v>156.0</v>
+      </c>
+      <c r="F17" t="n" s="26">
+        <v>7800.0</v>
+      </c>
+      <c r="G17" t="n" s="26">
+        <v>2886.0</v>
+      </c>
+      <c r="H17" t="n" s="26">
+        <v>4914.0</v>
+      </c>
+      <c r="I17" t="s" s="27">
+        <v>44</v>
+      </c>
+      <c r="J17" t="s" s="26">
+        <v>45</v>
+      </c>
+      <c r="K17" t="s" s="26">
+        <v>46</v>
+      </c>
+      <c r="L17" t="s" s="26">
+        <v>47</v>
+      </c>
+      <c r="M17" t="s" s="26">
+        <v>35</v>
+      </c>
+      <c r="N17" t="s" s="26">
+        <v>36</v>
+      </c>
+      <c r="O17" t="s" s="27">
+        <v>48</v>
+      </c>
+      <c r="P17" t="s" s="27">
+        <v>49</v>
+      </c>
+      <c r="Q17" t="s" s="27">
+        <v>50</v>
+      </c>
+      <c r="R17" t="s" s="27">
+        <v>51</v>
+      </c>
+      <c r="S17" t="s" s="26">
+        <v>41</v>
+      </c>
+      <c r="T17" t="s" s="26">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s" s="28">
+        <v>31</v>
+      </c>
+      <c r="B18" t="s" s="28">
+        <v>43</v>
+      </c>
+      <c r="C18" t="s" s="28">
+        <v>33</v>
+      </c>
+      <c r="D18" t="n" s="28">
+        <v>50.0</v>
+      </c>
+      <c r="E18" t="n" s="28">
+        <v>156.0</v>
+      </c>
+      <c r="F18" t="n" s="28">
+        <v>7800.0</v>
+      </c>
+      <c r="G18" t="n" s="28">
+        <v>2886.0</v>
+      </c>
+      <c r="H18" t="n" s="28">
+        <v>4914.0</v>
+      </c>
+      <c r="I18" t="s" s="29">
+        <v>44</v>
+      </c>
+      <c r="J18" t="s" s="28">
+        <v>45</v>
+      </c>
+      <c r="K18" t="s" s="28">
+        <v>46</v>
+      </c>
+      <c r="L18" t="s" s="28">
+        <v>47</v>
+      </c>
+      <c r="M18" t="s" s="28">
+        <v>35</v>
+      </c>
+      <c r="N18" t="s" s="28">
+        <v>36</v>
+      </c>
+      <c r="O18" t="s" s="29">
+        <v>48</v>
+      </c>
+      <c r="P18" t="s" s="29">
+        <v>49</v>
+      </c>
+      <c r="Q18" t="s" s="29">
+        <v>50</v>
+      </c>
+      <c r="R18" t="s" s="29">
+        <v>51</v>
+      </c>
+      <c r="S18" t="s" s="28">
+        <v>41</v>
+      </c>
+      <c r="T18" t="s" s="28">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s" s="30">
+        <v>31</v>
+      </c>
+      <c r="B19" t="s" s="30">
+        <v>43</v>
+      </c>
+      <c r="C19" t="s" s="30">
+        <v>33</v>
+      </c>
+      <c r="D19" t="n" s="30">
+        <v>50.0</v>
+      </c>
+      <c r="E19" t="n" s="30">
+        <v>156.0</v>
+      </c>
+      <c r="F19" t="n" s="30">
+        <v>7800.0</v>
+      </c>
+      <c r="G19" t="n" s="30">
+        <v>2886.0</v>
+      </c>
+      <c r="H19" t="n" s="30">
+        <v>4914.0</v>
+      </c>
+      <c r="I19" t="s" s="31">
+        <v>44</v>
+      </c>
+      <c r="J19" t="s" s="30">
+        <v>45</v>
+      </c>
+      <c r="K19" t="s" s="30">
+        <v>46</v>
+      </c>
+      <c r="L19" t="s" s="30">
+        <v>47</v>
+      </c>
+      <c r="M19" t="s" s="30">
+        <v>35</v>
+      </c>
+      <c r="N19" t="s" s="30">
+        <v>36</v>
+      </c>
+      <c r="O19" t="s" s="31">
+        <v>48</v>
+      </c>
+      <c r="P19" t="s" s="31">
+        <v>49</v>
+      </c>
+      <c r="Q19" t="s" s="31">
+        <v>50</v>
+      </c>
+      <c r="R19" t="s" s="31">
+        <v>51</v>
+      </c>
+      <c r="S19" t="s" s="30">
+        <v>41</v>
+      </c>
+      <c r="T19" t="s" s="30">
+        <v>42</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
